--- a/public/downloads/ZhangOff-equilibrium2025.xlsx
+++ b/public/downloads/ZhangOff-equilibrium2025.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="Allegro-OAM-L" sheetId="3" r:id="rId3"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="4" r:id="rId4"/>
-    <sheet name="CHGNetv0.3.0" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MatterSim_v1_5M" sheetId="10" r:id="rId10"/>
-    <sheet name="NequIP-OAM-L" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Allegro-OAM-L" sheetId="5" r:id="rId5"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="6" r:id="rId6"/>
+    <sheet name="CHGNetv0.3.0" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MatterSim_v1_5M" sheetId="12" r:id="rId12"/>
+    <sheet name="NequIP-OAM-L" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
@@ -656,10 +679,10 @@
         <v>10736</v>
       </c>
       <c r="N3" s="5">
-        <v>84704.10988354683</v>
+        <v>84704109.88354683</v>
       </c>
       <c r="O3" s="4">
-        <v>0.06768277248069443</v>
+        <v>67.68277248069442</v>
       </c>
       <c r="P3" s="5">
         <v>1251487</v>
@@ -694,7 +717,7 @@
         <v>1.496143719261758</v>
       </c>
       <c r="J4" s="4">
-        <v>3.378473673442599</v>
+        <v>3.378473673442598</v>
       </c>
       <c r="K4" s="4">
         <v>86.19680938694408</v>
@@ -706,10 +729,10 @@
         <v>10736</v>
       </c>
       <c r="N4" s="5">
-        <v>94417.59236001968</v>
+        <v>94417592.36001968</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04613169040655245</v>
+        <v>46.13169040655245</v>
       </c>
       <c r="P4" s="5">
         <v>2046697</v>
@@ -741,7 +764,7 @@
         <v>1.272228046773037</v>
       </c>
       <c r="I5" s="4">
-        <v>0.6405223095718892</v>
+        <v>0.640522309571889</v>
       </c>
       <c r="J5" s="4">
         <v>1.729582292588166</v>
@@ -756,10 +779,10 @@
         <v>10736</v>
       </c>
       <c r="N5" s="5">
-        <v>180982.6398518085</v>
+        <v>180982639.8518085</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1258309392003119</v>
+        <v>125.8309392003119</v>
       </c>
       <c r="P5" s="5">
         <v>1438300</v>
@@ -788,7 +811,7 @@
         <v>14.59575260804769</v>
       </c>
       <c r="H6" s="4">
-        <v>2.652384724865709</v>
+        <v>2.652384724865708</v>
       </c>
       <c r="I6" s="4">
         <v>1.144442465272933</v>
@@ -806,10 +829,10 @@
         <v>10736</v>
       </c>
       <c r="N6" s="5">
-        <v>276007.8381915092</v>
+        <v>276007838.1915092</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1166183819116122</v>
+        <v>116.6183819116122</v>
       </c>
       <c r="P6" s="5">
         <v>2366761</v>
@@ -856,10 +879,10 @@
         <v>8900</v>
       </c>
       <c r="N7" s="5">
-        <v>307425.679245472</v>
+        <v>307425679.245472</v>
       </c>
       <c r="O7" s="4">
-        <v>0.4403805223752662</v>
+        <v>440.3805223752662</v>
       </c>
       <c r="P7" s="5">
         <v>698091</v>
@@ -894,7 +917,7 @@
         <v>0.7455806890806667</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8426989776826062</v>
+        <v>0.8426989776826063</v>
       </c>
       <c r="K8" s="4">
         <v>91.3612919087157</v>
@@ -906,10 +929,10 @@
         <v>10736</v>
       </c>
       <c r="N8" s="5">
-        <v>39677.02971863747</v>
+        <v>39677029.71863747</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03010029102563152</v>
+        <v>30.10029102563152</v>
       </c>
       <c r="P8" s="5">
         <v>1318161</v>
@@ -944,7 +967,7 @@
         <v>1.116579492332975</v>
       </c>
       <c r="J9" s="4">
-        <v>19.3281738779938</v>
+        <v>19.32817387799379</v>
       </c>
       <c r="K9" s="4">
         <v>79.87936512160746</v>
@@ -956,10 +979,10 @@
         <v>10736</v>
       </c>
       <c r="N9" s="5">
-        <v>77536.62147378922</v>
+        <v>77536621.47378922</v>
       </c>
       <c r="O9" s="4">
-        <v>0.04204406928506742</v>
+        <v>42.04406928506742</v>
       </c>
       <c r="P9" s="5">
         <v>1844175</v>
@@ -1006,10 +1029,10 @@
         <v>10736</v>
       </c>
       <c r="N10" s="5">
-        <v>99679.45353746414</v>
+        <v>99679453.53746414</v>
       </c>
       <c r="O10" s="4">
-        <v>0.07519459086123033</v>
+        <v>75.19459086123032</v>
       </c>
       <c r="P10" s="5">
         <v>1325620</v>
@@ -1044,7 +1067,7 @@
         <v>0.4191937301286747</v>
       </c>
       <c r="J11" s="4">
-        <v>0.8518833882021086</v>
+        <v>0.8518833882021088</v>
       </c>
       <c r="K11" s="4">
         <v>89.92711913379345</v>
@@ -1056,10 +1079,10 @@
         <v>10736</v>
       </c>
       <c r="N11" s="5">
-        <v>79535.64137792587</v>
+        <v>79535641.37792587</v>
       </c>
       <c r="O11" s="4">
-        <v>0.06357470347332088</v>
+        <v>63.57470347332088</v>
       </c>
       <c r="P11" s="5">
         <v>1251058</v>
@@ -1106,10 +1129,10 @@
         <v>10736</v>
       </c>
       <c r="N12" s="5">
-        <v>40819.6231007576</v>
+        <v>40819623.1007576</v>
       </c>
       <c r="O12" s="4">
-        <v>0.03395074277355477</v>
+        <v>33.95074277355477</v>
       </c>
       <c r="P12" s="5">
         <v>1202319</v>
@@ -1156,10 +1179,10 @@
         <v>10736</v>
       </c>
       <c r="N13" s="5">
-        <v>94160.44471549988</v>
+        <v>94160444.71549988</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07337242306724258</v>
+        <v>73.37242306724258</v>
       </c>
       <c r="P13" s="5">
         <v>1283322</v>
@@ -1206,10 +1229,10 @@
         <v>10736</v>
       </c>
       <c r="N14" s="5">
-        <v>368601.40828228</v>
+        <v>368601408.28228</v>
       </c>
       <c r="O14" s="4">
-        <v>0.5624368226595561</v>
+        <v>562.4368226595561</v>
       </c>
       <c r="P14" s="5">
         <v>655365</v>
@@ -1238,13 +1261,13 @@
         <v>0.1024590163934426</v>
       </c>
       <c r="H15" s="4">
-        <v>0.5077620552962894</v>
+        <v>0.5077620552962895</v>
       </c>
       <c r="I15" s="4">
-        <v>0.492604604508039</v>
+        <v>0.4926046045080391</v>
       </c>
       <c r="J15" s="4">
-        <v>0.6337674128129294</v>
+        <v>0.6337674128129293</v>
       </c>
       <c r="K15" s="4">
         <v>91.18416833946694</v>
@@ -1256,10 +1279,10 @@
         <v>10736</v>
       </c>
       <c r="N15" s="5">
-        <v>531866.5926170349</v>
+        <v>531866592.6170349</v>
       </c>
       <c r="O15" s="4">
-        <v>0.5613367732105909</v>
+        <v>561.336773210591</v>
       </c>
       <c r="P15" s="5">
         <v>947500</v>
@@ -1306,10 +1329,10 @@
         <v>10736</v>
       </c>
       <c r="N16" s="5">
-        <v>175913.9782106876</v>
+        <v>175913978.2106876</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1166467153268419</v>
+        <v>116.6467153268419</v>
       </c>
       <c r="P16" s="5">
         <v>1508092</v>
@@ -1341,7 +1364,7 @@
         <v>0.7389125928561553</v>
       </c>
       <c r="I17" s="4">
-        <v>0.666230098557434</v>
+        <v>0.6662300985574341</v>
       </c>
       <c r="J17" s="4">
         <v>0.6128952843729635</v>
@@ -1356,10 +1379,10 @@
         <v>10736</v>
       </c>
       <c r="N17" s="5">
-        <v>154926.0289041996</v>
+        <v>154926028.9041996</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1221855543241605</v>
+        <v>122.1855543241605</v>
       </c>
       <c r="P17" s="5">
         <v>1267957</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,91 +1494,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.426579778300868</v>
+        <v>0.8464937254370122</v>
       </c>
       <c r="C3" s="4">
-        <v>0.9155291282631397</v>
+        <v>0.7368165115190035</v>
       </c>
       <c r="D3" s="4">
-        <v>1.349658227211351</v>
+        <v>0.8482150896633242</v>
       </c>
       <c r="E3" s="4">
-        <v>90.48134570043433</v>
+        <v>91.52610609635016</v>
       </c>
       <c r="F3" s="4">
-        <v>81.26300423578519</v>
+        <v>77.06554481280051</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>5191</v>
+        <v>3928</v>
       </c>
       <c r="I3" s="5">
-        <v>2285</v>
+        <v>5606</v>
       </c>
       <c r="J3" s="5">
-        <v>2533</v>
+        <v>475</v>
       </c>
       <c r="K3" s="5">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="M3" s="5">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>8</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2113782624738079</v>
+      </c>
+      <c r="O3" s="5">
+        <v>3936</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8032404870340714</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6732179222643434</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3918</v>
+      </c>
+      <c r="S3" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>5.738273133617674</v>
+        <v>1.16904766713286</v>
       </c>
       <c r="C4" s="4">
-        <v>1.380927352721216</v>
+        <v>0.8388752404687772</v>
       </c>
       <c r="D4" s="4">
-        <v>5.145526920174172</v>
+        <v>0.766755697331841</v>
       </c>
       <c r="E4" s="4">
-        <v>89.52614883642599</v>
+        <v>89.09220634608717</v>
       </c>
       <c r="F4" s="4">
-        <v>81.04543818025732</v>
+        <v>82.59903252310225</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>369</v>
       </c>
       <c r="I4" s="5">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="J4" s="5">
-        <v>391</v>
+        <v>63</v>
       </c>
       <c r="K4" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M4" s="5">
-        <v>344</v>
+        <v>25</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.8155276813667445</v>
+      </c>
+      <c r="O4" s="5">
+        <v>394</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7414454961892663</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6001322194767448</v>
+      </c>
+      <c r="R4" s="5">
+        <v>389</v>
+      </c>
+      <c r="S4" s="5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,66 +1735,100 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5179219572794781</v>
+        <v>3.752260874575739</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4191937301286747</v>
+        <v>1.116579492332975</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4944092212820863</v>
+        <v>3.038710330646476</v>
       </c>
       <c r="E3" s="4">
-        <v>90.20339177733266</v>
+        <v>83.74061643840292</v>
       </c>
       <c r="F3" s="4">
-        <v>87.12416207963153</v>
+        <v>72.50026653863874</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>8249</v>
+        <v>879</v>
       </c>
       <c r="I3" s="5">
-        <v>1371</v>
+        <v>5822</v>
       </c>
       <c r="J3" s="5">
-        <v>389</v>
+        <v>3308</v>
       </c>
       <c r="K3" s="5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L3" s="5">
-        <v>360</v>
+        <v>785</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2488</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-3.187690627829946</v>
+      </c>
+      <c r="O3" s="5">
+        <v>3367</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.336136711730304</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9560790932455088</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2694</v>
+      </c>
+      <c r="S3" s="5">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>5.457796945897253</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>7.334533509563682</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>5.773422503336225</v>
+        <v>243.5939794425046</v>
       </c>
       <c r="E4" s="4">
-        <v>86.12352506339529</v>
+        <v>26.71944155929221</v>
       </c>
       <c r="F4" s="4">
-        <v>84.89240512171914</v>
+        <v>50.62858303407398</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
@@ -1697,23 +1837,41 @@
         <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="J4" s="5">
-        <v>552</v>
+        <v>642</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>29</v>
+        <v>526</v>
       </c>
       <c r="M4" s="5">
-        <v>521</v>
+        <v>111</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-8.197244097329365</v>
+      </c>
+      <c r="O4" s="5">
+        <v>111</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.458867937463714</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9250824191780832</v>
+      </c>
+      <c r="R4" s="5">
+        <v>85</v>
+      </c>
+      <c r="S4" s="5">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1882,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1901,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1943,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,91 +1974,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.453475688866163</v>
+        <v>1.426579778300867</v>
       </c>
       <c r="C3" s="4">
-        <v>1.315926169118325</v>
+        <v>0.9155291282631397</v>
       </c>
       <c r="D3" s="4">
-        <v>1.528856000982393</v>
+        <v>1.34965822721135</v>
       </c>
       <c r="E3" s="4">
-        <v>87.91628010980607</v>
+        <v>90.48134570043433</v>
       </c>
       <c r="F3" s="4">
-        <v>90.25999195802063</v>
+        <v>81.26300423578519</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>7995</v>
+        <v>5191</v>
       </c>
       <c r="I3" s="5">
-        <v>506</v>
+        <v>2285</v>
       </c>
       <c r="J3" s="5">
-        <v>1508</v>
+        <v>2533</v>
       </c>
       <c r="K3" s="5">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="L3" s="5">
-        <v>89</v>
+        <v>533</v>
       </c>
       <c r="M3" s="5">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1929</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.283045460108345</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7120</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6774416579413177</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6574231414368105</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7112</v>
+      </c>
+      <c r="S3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>4.225154640269552</v>
+        <v>5.738273133617674</v>
       </c>
       <c r="C4" s="4">
-        <v>1.983039195650235</v>
+        <v>1.380927352721216</v>
       </c>
       <c r="D4" s="4">
-        <v>4.800195428887601</v>
+        <v>5.145526920174172</v>
       </c>
       <c r="E4" s="4">
-        <v>79.37217528001564</v>
+        <v>89.52614883642599</v>
       </c>
       <c r="F4" s="4">
-        <v>82.17016084611154</v>
+        <v>81.04543818025732</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>218</v>
+        <v>332</v>
       </c>
       <c r="J4" s="5">
-        <v>508</v>
+        <v>391</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M4" s="5">
-        <v>469</v>
+        <v>344</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-5.03627796427779</v>
+      </c>
+      <c r="O4" s="5">
+        <v>348</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.360934442976052</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7068280366459635</v>
+      </c>
+      <c r="R4" s="5">
+        <v>307</v>
+      </c>
+      <c r="S4" s="5">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2123,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2142,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2184,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,91 +2215,143 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.744350313126766</v>
+        <v>0.5179219572794781</v>
       </c>
       <c r="C3" s="4">
-        <v>1.256479387098264</v>
+        <v>0.4191937301286747</v>
       </c>
       <c r="D3" s="4">
-        <v>1.687234731454223</v>
+        <v>0.4944092212820863</v>
       </c>
       <c r="E3" s="4">
-        <v>91.75346269989684</v>
+        <v>90.20339177733266</v>
       </c>
       <c r="F3" s="4">
-        <v>78.84958347330786</v>
+        <v>87.12416207963153</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>4725</v>
+        <v>8249</v>
       </c>
       <c r="I3" s="5">
-        <v>4512</v>
+        <v>1371</v>
       </c>
       <c r="J3" s="5">
-        <v>772</v>
+        <v>389</v>
       </c>
       <c r="K3" s="5">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L3" s="5">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="M3" s="5">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3844146793413378</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8249</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.300745106864395</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2346293175403389</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8249</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>3.891345115462314</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.176087598891894</v>
-      </c>
+        <v>5.457796945897253</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>3.137620716930154</v>
+        <v>5.773422503336225</v>
       </c>
       <c r="E4" s="4">
-        <v>88.97308854766138</v>
+        <v>86.12352506339529</v>
       </c>
       <c r="F4" s="4">
-        <v>83.63170025448562</v>
+        <v>84.89240512171914</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
       </c>
       <c r="H4" s="5">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="J4" s="5">
-        <v>435</v>
+        <v>552</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
         <v>29</v>
       </c>
       <c r="M4" s="5">
-        <v>403</v>
+        <v>521</v>
+      </c>
+      <c r="N4" s="4">
+        <v>5.511207095576</v>
+      </c>
+      <c r="O4" s="5">
+        <v>521</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5589266003509595</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5212245269800118</v>
+      </c>
+      <c r="R4" s="5">
+        <v>521</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2362,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2381,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2423,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,91 +2454,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.715145358116296</v>
+        <v>1.453475688866163</v>
       </c>
       <c r="C3" s="4">
-        <v>1.315797451039004</v>
+        <v>1.315926169118325</v>
       </c>
       <c r="D3" s="4">
-        <v>1.720867911024505</v>
+        <v>1.528856000982393</v>
       </c>
       <c r="E3" s="4">
-        <v>97.37053318679858</v>
+        <v>87.91628010980607</v>
       </c>
       <c r="F3" s="4">
-        <v>96.09559114917371</v>
+        <v>90.25999195802063</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>6302</v>
+        <v>7995</v>
       </c>
       <c r="I3" s="5">
-        <v>84</v>
+        <v>506</v>
       </c>
       <c r="J3" s="5">
-        <v>3623</v>
+        <v>1508</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L3" s="5">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="M3" s="5">
-        <v>3565</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1410</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.451938877344592</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9405</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4220154667241661</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4183455764878601</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9405</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>14.64843262929731</v>
+        <v>4.225154640269552</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>1.983039195650235</v>
       </c>
       <c r="D4" s="4">
-        <v>8.804893956620425</v>
+        <v>4.800195428887601</v>
       </c>
       <c r="E4" s="4">
-        <v>90.79279304569134</v>
+        <v>79.37217528001564</v>
       </c>
       <c r="F4" s="4">
-        <v>90.84889635626871</v>
+        <v>82.17016084611154</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="J4" s="5">
-        <v>727</v>
+        <v>508</v>
       </c>
       <c r="K4" s="5">
-        <v>727</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>469</v>
+      </c>
+      <c r="N4" s="4">
+        <v>4.134304405350816</v>
+      </c>
+      <c r="O4" s="5">
+        <v>470</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8488539567798389</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.803289567256825</v>
+      </c>
+      <c r="R4" s="5">
+        <v>452</v>
+      </c>
+      <c r="S4" s="5">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2603,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2611,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2622,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2664,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,91 +2695,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5279860453259598</v>
+        <v>1.744350313126766</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5125394746785944</v>
+        <v>1.256479387098264</v>
       </c>
       <c r="D3" s="4">
-        <v>0.567751641906598</v>
+        <v>1.687234731454223</v>
       </c>
       <c r="E3" s="4">
-        <v>91.83364903559591</v>
+        <v>91.75346269989684</v>
       </c>
       <c r="F3" s="4">
-        <v>93.2163804254026</v>
+        <v>78.84958347330786</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>9763</v>
+        <v>4725</v>
       </c>
       <c r="I3" s="5">
-        <v>180</v>
+        <v>4512</v>
       </c>
       <c r="J3" s="5">
-        <v>66</v>
+        <v>772</v>
       </c>
       <c r="K3" s="5">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L3" s="5">
-        <v>49</v>
+        <v>350</v>
       </c>
       <c r="M3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>406</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.333578530714477</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5131</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6131189730239349</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3755385079974542</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5128</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2293275075563035</v>
+        <v>3.891345115462314</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1972720741967615</v>
+        <v>1.176087598891894</v>
       </c>
       <c r="D4" s="4">
-        <v>1.542642035923619</v>
+        <v>3.137620716930154</v>
       </c>
       <c r="E4" s="4">
-        <v>82.24241828781022</v>
+        <v>88.97308854766138</v>
       </c>
       <c r="F4" s="4">
-        <v>88.06016881610239</v>
+        <v>83.63170025448562</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
       </c>
       <c r="H4" s="5">
-        <v>659</v>
+        <v>46</v>
       </c>
       <c r="I4" s="5">
-        <v>60</v>
+        <v>246</v>
       </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>435</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>403</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-3.492783648038268</v>
+      </c>
+      <c r="O4" s="5">
+        <v>449</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9757129182466029</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6715948100536716</v>
+      </c>
+      <c r="R4" s="5">
+        <v>419</v>
+      </c>
+      <c r="S4" s="5">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2844,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2863,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2905,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,91 +2936,139 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.31737277778013</v>
+        <v>1.715145358116296</v>
       </c>
       <c r="C3" s="4">
-        <v>1.079105634622018</v>
+        <v>1.315797451039004</v>
       </c>
       <c r="D3" s="4">
-        <v>1.821599864057597</v>
+        <v>1.720867911024505</v>
       </c>
       <c r="E3" s="4">
-        <v>90.69626451839582</v>
+        <v>97.37053318679858</v>
       </c>
       <c r="F3" s="4">
-        <v>78.39360906280538</v>
+        <v>96.09559114917371</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>4031</v>
+        <v>6302</v>
       </c>
       <c r="I3" s="5">
-        <v>5239</v>
+        <v>84</v>
       </c>
       <c r="J3" s="5">
-        <v>739</v>
+        <v>3623</v>
       </c>
       <c r="K3" s="5">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>497</v>
+        <v>56</v>
       </c>
       <c r="M3" s="5">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>3565</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.711483991102156</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9867</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5510694338263112</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5477384715728466</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9859</v>
+      </c>
+      <c r="S3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.554954926701585</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.838119870286526</v>
-      </c>
+        <v>14.64843262929731</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>2.828006282750334</v>
+        <v>8.804893956620425</v>
       </c>
       <c r="E4" s="4">
-        <v>88.63641467591155</v>
+        <v>90.79279304569134</v>
       </c>
       <c r="F4" s="4">
-        <v>85.44221141093455</v>
+        <v>90.84889635626871</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
       </c>
       <c r="H4" s="5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>513</v>
+        <v>727</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>727</v>
       </c>
       <c r="L4" s="5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>481</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>14.64843262929731</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3079,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3087,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3098,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3140,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,91 +3171,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6878457657461859</v>
+        <v>0.5279860453259598</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6262293654608844</v>
+        <v>0.5125394746785944</v>
       </c>
       <c r="D3" s="4">
-        <v>0.537143892438628</v>
+        <v>0.5677516419065979</v>
       </c>
       <c r="E3" s="4">
-        <v>91.51936726334053</v>
+        <v>91.83364903559591</v>
       </c>
       <c r="F3" s="4">
-        <v>88.20843232142522</v>
+        <v>93.2163804254026</v>
       </c>
       <c r="G3" s="5">
         <v>10009</v>
       </c>
       <c r="H3" s="5">
-        <v>7849</v>
+        <v>9763</v>
       </c>
       <c r="I3" s="5">
-        <v>1885</v>
+        <v>180</v>
       </c>
       <c r="J3" s="5">
-        <v>275</v>
+        <v>66</v>
       </c>
       <c r="K3" s="5">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>236</v>
+        <v>49</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>11</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.5041476689181352</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9774</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2471684690726207</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2383586617098033</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9774</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.441977066781442</v>
+        <v>0.2293275075563035</v>
       </c>
       <c r="C4" s="4">
-        <v>1.337097094443798</v>
+        <v>0.1972720741967615</v>
       </c>
       <c r="D4" s="4">
-        <v>1.655805438252969</v>
+        <v>1.542642035923619</v>
       </c>
       <c r="E4" s="4">
-        <v>83.32261928155022</v>
+        <v>82.24241828781022</v>
       </c>
       <c r="F4" s="4">
-        <v>86.05211574027039</v>
+        <v>88.06016881610239</v>
       </c>
       <c r="G4" s="5">
         <v>727</v>
       </c>
       <c r="H4" s="5">
-        <v>468</v>
+        <v>659</v>
       </c>
       <c r="I4" s="5">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="J4" s="5">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
-        <v>99</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.08546814202637566</v>
+      </c>
+      <c r="O4" s="5">
+        <v>659</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2248397046748344</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1871050905855445</v>
+      </c>
+      <c r="R4" s="5">
+        <v>659</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3320,1352 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.31737277778013</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.079105634622018</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.821599864057597</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.69626451839582</v>
+      </c>
+      <c r="F3" s="4">
+        <v>78.39360906280538</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10009</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4031</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5239</v>
+      </c>
+      <c r="J3" s="5">
+        <v>739</v>
+      </c>
+      <c r="K3" s="5">
+        <v>24</v>
+      </c>
+      <c r="L3" s="5">
+        <v>497</v>
+      </c>
+      <c r="M3" s="5">
+        <v>218</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.134845583634015</v>
+      </c>
+      <c r="O3" s="5">
+        <v>4249</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4759429741647837</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4205565030959294</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4249</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2.554954926701585</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.838119870286526</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.828006282750334</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.63641467591155</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.44221141093455</v>
+      </c>
+      <c r="G4" s="5">
+        <v>727</v>
+      </c>
+      <c r="H4" s="5">
+        <v>38</v>
+      </c>
+      <c r="I4" s="5">
+        <v>176</v>
+      </c>
+      <c r="J4" s="5">
+        <v>513</v>
+      </c>
+      <c r="K4" s="5">
+        <v>4</v>
+      </c>
+      <c r="L4" s="5">
+        <v>28</v>
+      </c>
+      <c r="M4" s="5">
+        <v>481</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2.664383831707113</v>
+      </c>
+      <c r="O4" s="5">
+        <v>519</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4988333099915616</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3890546558856227</v>
+      </c>
+      <c r="R4" s="5">
+        <v>517</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6878457657461858</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6262293654608844</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5371438924386279</v>
+      </c>
+      <c r="E3" s="4">
+        <v>91.51936726334053</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.20843232142522</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10009</v>
+      </c>
+      <c r="H3" s="5">
+        <v>7849</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1885</v>
+      </c>
+      <c r="J3" s="5">
+        <v>275</v>
+      </c>
+      <c r="K3" s="5">
+        <v>39</v>
+      </c>
+      <c r="L3" s="5">
+        <v>236</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.03773676802866564</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7849</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6809044259481564</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6223462387621174</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7849</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.441977066781442</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.337097094443798</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.655805438252969</v>
+      </c>
+      <c r="E4" s="4">
+        <v>83.32261928155022</v>
+      </c>
+      <c r="F4" s="4">
+        <v>86.05211574027039</v>
+      </c>
+      <c r="G4" s="5">
+        <v>727</v>
+      </c>
+      <c r="H4" s="5">
+        <v>468</v>
+      </c>
+      <c r="I4" s="5">
+        <v>139</v>
+      </c>
+      <c r="J4" s="5">
+        <v>120</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>19</v>
+      </c>
+      <c r="M4" s="5">
+        <v>99</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.513005900263611</v>
+      </c>
+      <c r="O4" s="5">
+        <v>567</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4773051428671483</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4265510716926407</v>
+      </c>
+      <c r="R4" s="5">
+        <v>566</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>83.9139344262295</v>
+      </c>
+      <c r="C3" s="3">
+        <v>11.54061102831595</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.024590163934426</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.906110283159463</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.6147540983606558</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.6115585570972248</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.5491813127938447</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.6517483021399869</v>
+      </c>
+      <c r="K3" s="4">
+        <v>94.26126542271162</v>
+      </c>
+      <c r="L3" s="4">
+        <v>90.10955008885198</v>
+      </c>
+      <c r="M3" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N3" s="5">
+        <v>84704109.88354683</v>
+      </c>
+      <c r="O3" s="4">
+        <v>67.68277248069442</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1251487</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>55.73770491803278</v>
+      </c>
+      <c r="C4" s="3">
+        <v>13.9623695976155</v>
+      </c>
+      <c r="D4" s="3">
+        <v>30.29992548435171</v>
+      </c>
+      <c r="E4" s="3">
+        <v>24.69262295081967</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3.874813710879284</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.732488822652757</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.826994401907252</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.7069916318878025</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.008459968551259</v>
+      </c>
+      <c r="K4" s="4">
+        <v>86.19680938694408</v>
+      </c>
+      <c r="L4" s="4">
+        <v>79.81325244968103</v>
+      </c>
+      <c r="M4" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N4" s="5">
+        <v>94417592.36001968</v>
+      </c>
+      <c r="O4" s="4">
+        <v>46.13169040655245</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2046697</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>82.38636363636364</v>
+      </c>
+      <c r="C5" s="3">
+        <v>15.58308494783905</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.030551415797317</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.1956035767511178</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.192250372578241</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.6426974664679582</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.6254163401546194</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.576275611808213</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.031345925306566</v>
+      </c>
+      <c r="K5" s="4">
+        <v>82.73282971907076</v>
+      </c>
+      <c r="L5" s="4">
+        <v>84.95719205199752</v>
+      </c>
+      <c r="M5" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N5" s="5">
+        <v>180982639.8518085</v>
+      </c>
+      <c r="O5" s="4">
+        <v>125.8309392003119</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1438300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>31.18479880774963</v>
+      </c>
+      <c r="C6" s="3">
+        <v>48.15573770491803</v>
+      </c>
+      <c r="D6" s="3">
+        <v>20.65946348733234</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.1210879284649776</v>
+      </c>
+      <c r="F6" s="3">
+        <v>20.14716840536513</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.3912071535022355</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.9787309435930821</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.8581527835101418</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1.300796609443142</v>
+      </c>
+      <c r="K6" s="4">
+        <v>76.7875898496506</v>
+      </c>
+      <c r="L6" s="4">
+        <v>67.44948626711609</v>
+      </c>
+      <c r="M6" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N6" s="5">
+        <v>276007838.1915092</v>
+      </c>
+      <c r="O6" s="4">
+        <v>116.6183819116122</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2366761</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>84.70786516853933</v>
+      </c>
+      <c r="C7" s="3">
+        <v>13.30337078651685</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.98876404494382</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.3707865168539326</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.606741573033708</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2607768906587983</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2297382668046554</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2123045354288413</v>
+      </c>
+      <c r="K7" s="4">
+        <v>97.00264083161358</v>
+      </c>
+      <c r="L7" s="4">
+        <v>92.21150617097757</v>
+      </c>
+      <c r="M7" s="5">
+        <v>8900</v>
+      </c>
+      <c r="N7" s="5">
+        <v>307425679.245472</v>
+      </c>
+      <c r="O7" s="4">
+        <v>440.3805223752662</v>
+      </c>
+      <c r="P7" s="5">
+        <v>698091</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>40.11736214605067</v>
+      </c>
+      <c r="C8" s="3">
+        <v>54.96460506706408</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4.918032786885246</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.02794336810730253</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.67585692995529</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.2142324888226528</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.7990559715400165</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.6666169614135479</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.8266286954237543</v>
+      </c>
+      <c r="K8" s="4">
+        <v>91.3612919087157</v>
+      </c>
+      <c r="L8" s="4">
+        <v>77.44025099437543</v>
+      </c>
+      <c r="M8" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N8" s="5">
+        <v>39677029.71863747</v>
+      </c>
+      <c r="O8" s="4">
+        <v>30.10029102563152</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1318161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>25.88487332339791</v>
+      </c>
+      <c r="C9" s="3">
+        <v>55.02049180327869</v>
+      </c>
+      <c r="D9" s="3">
+        <v>19.0946348733234</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.3725782414307005</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12.21125186289121</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6.510804769001491</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1.344447591118175</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.9551310121747165</v>
+      </c>
+      <c r="J9" s="4">
+        <v>17.12867365336112</v>
+      </c>
+      <c r="K9" s="4">
+        <v>79.87936512160746</v>
+      </c>
+      <c r="L9" s="4">
+        <v>71.0192015323217</v>
+      </c>
+      <c r="M9" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N9" s="5">
+        <v>77536621.47378922</v>
+      </c>
+      <c r="O9" s="4">
+        <v>42.04406928506742</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1844175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>69.10394932935915</v>
+      </c>
+      <c r="C10" s="3">
+        <v>24.37593144560358</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6.520119225037257</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.7265275707898659</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5.337183308494784</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.456408345752608</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.7237251205642919</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.6594675278540107</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1.005838270807564</v>
+      </c>
+      <c r="K10" s="4">
+        <v>90.41666349848437</v>
+      </c>
+      <c r="L10" s="4">
+        <v>81.24827151201764</v>
+      </c>
+      <c r="M10" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N10" s="5">
+        <v>99679453.53746414</v>
+      </c>
+      <c r="O10" s="4">
+        <v>75.19459086123032</v>
+      </c>
+      <c r="P10" s="5">
+        <v>1325620</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>81.68777943368107</v>
+      </c>
+      <c r="C11" s="3">
+        <v>14.40014903129657</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.912071535022354</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.2887481371087929</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.623323397913562</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3182281495026898</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2516550990817379</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.292103242559304</v>
+      </c>
+      <c r="K11" s="4">
+        <v>89.92711913379345</v>
+      </c>
+      <c r="L11" s="4">
+        <v>86.97303621260463</v>
+      </c>
+      <c r="M11" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N11" s="5">
+        <v>79535641.37792587</v>
+      </c>
+      <c r="O11" s="4">
+        <v>63.57470347332088</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1251058</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>91.81259314456037</v>
+      </c>
+      <c r="C12" s="3">
+        <v>6.743666169895677</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.443740685543964</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.1397168405365127</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.1676602086438152</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4509193026286439</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.4359974669035618</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.4701596700777561</v>
+      </c>
+      <c r="K12" s="4">
+        <v>87.33770669221499</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.71218018283841</v>
+      </c>
+      <c r="M12" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N12" s="5">
+        <v>40819623.1007576</v>
+      </c>
+      <c r="O12" s="4">
+        <v>33.95074277355477</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1202319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>51.66728763040238</v>
+      </c>
+      <c r="C13" s="3">
+        <v>44.31818181818182</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4.014530551415797</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.1769746646795827</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.530178837555887</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.3073770491803279</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.6376724192028543</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3979015133267413</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.5504132639306648</v>
+      </c>
+      <c r="K13" s="4">
+        <v>91.56518661861153</v>
+      </c>
+      <c r="L13" s="4">
+        <v>79.17340974938078</v>
+      </c>
+      <c r="M13" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N13" s="5">
+        <v>94160444.71549988</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.37242306724258</v>
+      </c>
+      <c r="P13" s="5">
+        <v>1283322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>91.83122205663189</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.782414307004471</v>
+      </c>
+      <c r="D14" s="3">
+        <v>7.386363636363637</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.790238450074515</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.5216095380029807</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.07451564828614009</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.505687824577747</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.5477384715728466</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1.114563672323896</v>
+      </c>
+      <c r="K14" s="4">
+        <v>96.92511430801835</v>
+      </c>
+      <c r="L14" s="4">
+        <v>95.7403054641473</v>
+      </c>
+      <c r="M14" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N14" s="5">
+        <v>368601408.28228</v>
+      </c>
+      <c r="O14" s="4">
+        <v>562.4368226595561</v>
+      </c>
+      <c r="P14" s="5">
+        <v>655365</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>97.17771982116244</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.235469448584203</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.5868107302533532</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.05588673621460507</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.5309239940387481</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2456564523329421</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2351212320758642</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3729896182993048</v>
+      </c>
+      <c r="K15" s="4">
+        <v>91.18416833946694</v>
+      </c>
+      <c r="L15" s="4">
+        <v>92.8672219082672</v>
+      </c>
+      <c r="M15" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N15" s="5">
+        <v>531866592.6170349</v>
+      </c>
+      <c r="O15" s="4">
+        <v>561.336773210591</v>
+      </c>
+      <c r="P15" s="5">
+        <v>947500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>44.39269746646796</v>
+      </c>
+      <c r="C16" s="3">
+        <v>50.43777943368107</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5.169523099850968</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.2608047690014904</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4.890089418777944</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.01862891207153502</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4774930183289108</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.4171392863507073</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.8082977110163694</v>
+      </c>
+      <c r="K16" s="4">
+        <v>90.55677952999359</v>
+      </c>
+      <c r="L16" s="4">
+        <v>78.87091289170728</v>
+      </c>
+      <c r="M16" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N16" s="5">
+        <v>175913978.2106876</v>
+      </c>
+      <c r="O16" s="4">
+        <v>116.6467153268419</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1508092</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>78.3811475409836</v>
+      </c>
+      <c r="C17" s="3">
+        <v>18.85245901639344</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.766393442622951</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.381892697466468</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.375186289120715</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.009314456035767511</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.6671174774757372</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.6091768906264877</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.5294219597422392</v>
+      </c>
+      <c r="K17" s="4">
+        <v>90.96431549519956</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.06241498214615</v>
+      </c>
+      <c r="M17" s="5">
+        <v>10736</v>
+      </c>
+      <c r="N17" s="5">
+        <v>154926028.9041996</v>
+      </c>
+      <c r="O17" s="4">
+        <v>122.1855543241605</v>
+      </c>
+      <c r="P17" s="5">
+        <v>1267957</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2875,10 +4779,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="L3" s="5">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -2919,10 +4823,10 @@
         <v>2636</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>544</v>
+        <v>415</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -2963,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -3007,10 +4911,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L6" s="5">
-        <v>2166</v>
+        <v>2159</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -3051,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="L7" s="5">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -3095,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5">
         <v>499</v>
@@ -3139,10 +5043,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L9" s="5">
-        <v>1325</v>
+        <v>1307</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
@@ -3183,10 +5087,10 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="L10" s="5">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -3227,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L11" s="5">
         <v>374</v>
@@ -3271,10 +5175,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L12" s="5">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -3315,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L13" s="5">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -3359,10 +5263,10 @@
         <v>0</v>
       </c>
       <c r="K14" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
@@ -3403,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L15" s="5">
         <v>51</v>
@@ -3447,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="L16" s="5">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
@@ -3491,10 +5395,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="L17" s="5">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
@@ -3516,9 +5420,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>9009</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1239</v>
+      </c>
+      <c r="D3" s="5">
+        <v>488</v>
+      </c>
+      <c r="E3" s="5">
+        <v>110</v>
+      </c>
+      <c r="F3" s="5">
+        <v>312</v>
+      </c>
+      <c r="G3" s="5">
+        <v>66</v>
+      </c>
+      <c r="H3" s="5">
+        <v>110</v>
+      </c>
+      <c r="I3" s="5">
+        <v>110</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>77</v>
+      </c>
+      <c r="L3" s="5">
+        <v>235</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>5984</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1499</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3253</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2651</v>
+      </c>
+      <c r="F4" s="5">
+        <v>416</v>
+      </c>
+      <c r="G4" s="5">
+        <v>186</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2651</v>
+      </c>
+      <c r="I4" s="5">
+        <v>14</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2636</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>415</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>8845</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1673</v>
+      </c>
+      <c r="D5" s="5">
+        <v>218</v>
+      </c>
+      <c r="E5" s="5">
+        <v>21</v>
+      </c>
+      <c r="F5" s="5">
+        <v>128</v>
+      </c>
+      <c r="G5" s="5">
+        <v>69</v>
+      </c>
+      <c r="H5" s="5">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5">
+        <v>21</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>126</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3348</v>
+      </c>
+      <c r="C6" s="5">
+        <v>5170</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2218</v>
+      </c>
+      <c r="E6" s="5">
+        <v>13</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2163</v>
+      </c>
+      <c r="G6" s="5">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5">
+        <v>13</v>
+      </c>
+      <c r="I6" s="5">
+        <v>13</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>4</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2159</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>7539</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1184</v>
+      </c>
+      <c r="D7" s="5">
+        <v>177</v>
+      </c>
+      <c r="E7" s="5">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5">
+        <v>143</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>33</v>
+      </c>
+      <c r="I7" s="5">
+        <v>33</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>42</v>
+      </c>
+      <c r="L7" s="5">
+        <v>101</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4307</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5901</v>
+      </c>
+      <c r="D8" s="5">
+        <v>528</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3</v>
+      </c>
+      <c r="F8" s="5">
+        <v>502</v>
+      </c>
+      <c r="G8" s="5">
+        <v>23</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>3</v>
+      </c>
+      <c r="L8" s="5">
+        <v>499</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2779</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5907</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2050</v>
+      </c>
+      <c r="E9" s="5">
+        <v>40</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1311</v>
+      </c>
+      <c r="G9" s="5">
+        <v>699</v>
+      </c>
+      <c r="H9" s="5">
+        <v>40</v>
+      </c>
+      <c r="I9" s="5">
+        <v>40</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>5</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1307</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>7419</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2617</v>
+      </c>
+      <c r="D10" s="5">
+        <v>700</v>
+      </c>
+      <c r="E10" s="5">
+        <v>78</v>
+      </c>
+      <c r="F10" s="5">
+        <v>573</v>
+      </c>
+      <c r="G10" s="5">
+        <v>49</v>
+      </c>
+      <c r="H10" s="5">
+        <v>78</v>
+      </c>
+      <c r="I10" s="5">
+        <v>78</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>7</v>
+      </c>
+      <c r="L10" s="5">
+        <v>566</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>8770</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1546</v>
+      </c>
+      <c r="D11" s="5">
+        <v>420</v>
+      </c>
+      <c r="E11" s="5">
+        <v>31</v>
+      </c>
+      <c r="F11" s="5">
+        <v>389</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>31</v>
+      </c>
+      <c r="I11" s="5">
+        <v>31</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>15</v>
+      </c>
+      <c r="L11" s="5">
+        <v>374</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>9857</v>
+      </c>
+      <c r="C12" s="5">
+        <v>724</v>
+      </c>
+      <c r="D12" s="5">
+        <v>155</v>
+      </c>
+      <c r="E12" s="5">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5">
+        <v>122</v>
+      </c>
+      <c r="G12" s="5">
+        <v>18</v>
+      </c>
+      <c r="H12" s="5">
+        <v>15</v>
+      </c>
+      <c r="I12" s="5">
+        <v>15</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>15</v>
+      </c>
+      <c r="L12" s="5">
+        <v>107</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>5547</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4758</v>
+      </c>
+      <c r="D13" s="5">
+        <v>431</v>
+      </c>
+      <c r="E13" s="5">
+        <v>19</v>
+      </c>
+      <c r="F13" s="5">
+        <v>379</v>
+      </c>
+      <c r="G13" s="5">
+        <v>33</v>
+      </c>
+      <c r="H13" s="5">
+        <v>19</v>
+      </c>
+      <c r="I13" s="5">
+        <v>19</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>17</v>
+      </c>
+      <c r="L13" s="5">
+        <v>363</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>9859</v>
+      </c>
+      <c r="C14" s="5">
+        <v>84</v>
+      </c>
+      <c r="D14" s="5">
+        <v>793</v>
+      </c>
+      <c r="E14" s="5">
+        <v>729</v>
+      </c>
+      <c r="F14" s="5">
+        <v>56</v>
+      </c>
+      <c r="G14" s="5">
+        <v>8</v>
+      </c>
+      <c r="H14" s="5">
+        <v>729</v>
+      </c>
+      <c r="I14" s="5">
+        <v>6</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>4</v>
+      </c>
+      <c r="L14" s="5">
+        <v>52</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>10433</v>
+      </c>
+      <c r="C15" s="5">
+        <v>240</v>
+      </c>
+      <c r="D15" s="5">
+        <v>63</v>
+      </c>
+      <c r="E15" s="5">
+        <v>6</v>
+      </c>
+      <c r="F15" s="5">
+        <v>57</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>6</v>
+      </c>
+      <c r="I15" s="5">
+        <v>6</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>6</v>
+      </c>
+      <c r="L15" s="5">
+        <v>51</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>4766</v>
+      </c>
+      <c r="C16" s="5">
+        <v>5415</v>
+      </c>
+      <c r="D16" s="5">
+        <v>555</v>
+      </c>
+      <c r="E16" s="5">
+        <v>28</v>
+      </c>
+      <c r="F16" s="5">
+        <v>525</v>
+      </c>
+      <c r="G16" s="5">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>28</v>
+      </c>
+      <c r="I16" s="5">
+        <v>28</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>11</v>
+      </c>
+      <c r="L16" s="5">
+        <v>514</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>8415</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2024</v>
+      </c>
+      <c r="D17" s="5">
+        <v>297</v>
+      </c>
+      <c r="E17" s="5">
+        <v>41</v>
+      </c>
+      <c r="F17" s="5">
+        <v>255</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>41</v>
+      </c>
+      <c r="I17" s="5">
+        <v>41</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>28</v>
+      </c>
+      <c r="L17" s="5">
+        <v>228</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6188,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6230,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,13 +6261,31 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.674025474165315</v>
+        <v>1.674025474165316</v>
       </c>
       <c r="C3" s="4">
         <v>1.272223387535657</v>
@@ -3629,17 +6320,33 @@
       <c r="M3" s="5">
         <v>2275</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.55341118195192</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8555</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5863262991227632</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5327433027602524</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8525</v>
+      </c>
+      <c r="S3" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>6.002018147435344</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>6.451427407987562</v>
       </c>
@@ -3670,9 +6377,27 @@
       <c r="M4" s="5">
         <v>520</v>
       </c>
+      <c r="N4" s="4">
+        <v>5.961245578905347</v>
+      </c>
+      <c r="O4" s="5">
+        <v>520</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9589446232132994</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8387144440673466</v>
+      </c>
+      <c r="R4" s="5">
+        <v>484</v>
+      </c>
+      <c r="S4" s="5">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6408,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6427,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6469,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6500,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>2.999973271721941</v>
@@ -3801,10 +6559,28 @@
       <c r="M3" s="5">
         <v>4865</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-2.885464126138628</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5920</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.820886136153642</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7185852724925366</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5736</v>
+      </c>
+      <c r="S3" s="5">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>2.230214212514453</v>
@@ -3842,9 +6618,27 @@
       <c r="M4" s="5">
         <v>236</v>
       </c>
+      <c r="N4" s="4">
+        <v>2.862357054948811</v>
+      </c>
+      <c r="O4" s="5">
+        <v>250</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9110901817255218</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4388419443524996</v>
+      </c>
+      <c r="R4" s="5">
+        <v>248</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6649,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6668,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6710,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,19 +6741,37 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.68506991641995</v>
+        <v>0.6850699164199497</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6405223095718892</v>
+        <v>0.640522309571889</v>
       </c>
       <c r="D3" s="4">
-        <v>1.095803402763191</v>
+        <v>1.095803402763192</v>
       </c>
       <c r="E3" s="4">
         <v>83.1512251218801</v>
@@ -3973,17 +6800,33 @@
       <c r="M3" s="5">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2899343001694845</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8607</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5918375238299109</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5659406809410051</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8570</v>
+      </c>
+      <c r="S3" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>9.35594981665481</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>10.45515713200793</v>
       </c>
@@ -4014,9 +6857,27 @@
       <c r="M4" s="5">
         <v>307</v>
       </c>
+      <c r="N4" s="4">
+        <v>9.143691949241109</v>
+      </c>
+      <c r="O4" s="5">
+        <v>307</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.087713964080351</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8983496391971995</v>
+      </c>
+      <c r="R4" s="5">
+        <v>275</v>
+      </c>
+      <c r="S4" s="5">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6888,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6907,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6949,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,13 +6980,31 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.437158375826462</v>
+        <v>2.437158375826461</v>
       </c>
       <c r="C3" s="4">
         <v>1.144442465272933</v>
@@ -4145,17 +7039,33 @@
       <c r="M3" s="5">
         <v>1413</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.909523165613009</v>
+      </c>
+      <c r="O3" s="5">
+        <v>3236</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9798017391225705</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8578885945442692</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3218</v>
+      </c>
+      <c r="S3" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>5.615521626562848</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>7.81150112728383</v>
       </c>
@@ -4186,9 +7096,27 @@
       <c r="M4" s="5">
         <v>154</v>
       </c>
+      <c r="N4" s="4">
+        <v>5.721900252584998</v>
+      </c>
+      <c r="O4" s="5">
+        <v>154</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.963988725636205</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8646924765268945</v>
+      </c>
+      <c r="R4" s="5">
+        <v>130</v>
+      </c>
+      <c r="S4" s="5">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7127,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7146,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7188,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7219,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3897102799316191</v>
@@ -4317,10 +7278,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3567219073480565</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6878</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2663381972943886</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2371016195117367</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6878</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.141964605181243</v>
@@ -4358,9 +7337,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>1.161887410235063</v>
+      </c>
+      <c r="O4" s="5">
+        <v>662</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1982561765835863</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1531192956710621</v>
+      </c>
+      <c r="R4" s="5">
+        <v>661</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7368,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8464937254370124</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7368165115190035</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.8482150896633242</v>
-      </c>
-      <c r="E3" s="4">
-        <v>91.52610609635016</v>
-      </c>
-      <c r="F3" s="4">
-        <v>77.06554481280051</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10009</v>
-      </c>
-      <c r="H3" s="5">
-        <v>3928</v>
-      </c>
-      <c r="I3" s="5">
-        <v>5606</v>
-      </c>
-      <c r="J3" s="5">
-        <v>475</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>466</v>
-      </c>
-      <c r="M3" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.16904766713286</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.8388752404687772</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.766755697331841</v>
-      </c>
-      <c r="E4" s="4">
-        <v>89.09220634608717</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.59903252310225</v>
-      </c>
-      <c r="G4" s="5">
-        <v>727</v>
-      </c>
-      <c r="H4" s="5">
-        <v>369</v>
-      </c>
-      <c r="I4" s="5">
-        <v>295</v>
-      </c>
-      <c r="J4" s="5">
-        <v>63</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>36</v>
-      </c>
-      <c r="M4" s="5">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>3.75226087457574</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.116579492332975</v>
-      </c>
-      <c r="D3" s="4">
-        <v>3.038710330646476</v>
-      </c>
-      <c r="E3" s="4">
-        <v>83.74061643840292</v>
-      </c>
-      <c r="F3" s="4">
-        <v>72.50026653863874</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10009</v>
-      </c>
-      <c r="H3" s="5">
-        <v>879</v>
-      </c>
-      <c r="I3" s="5">
-        <v>5822</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3308</v>
-      </c>
-      <c r="K3" s="5">
-        <v>35</v>
-      </c>
-      <c r="L3" s="5">
-        <v>785</v>
-      </c>
-      <c r="M3" s="5">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>7.334533509563682</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>243.5939794425046</v>
-      </c>
-      <c r="E4" s="4">
-        <v>26.71944155929221</v>
-      </c>
-      <c r="F4" s="4">
-        <v>50.62858303407398</v>
-      </c>
-      <c r="G4" s="5">
-        <v>727</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>85</v>
-      </c>
-      <c r="J4" s="5">
-        <v>642</v>
-      </c>
-      <c r="K4" s="5">
-        <v>5</v>
-      </c>
-      <c r="L4" s="5">
-        <v>526</v>
-      </c>
-      <c r="M4" s="5">
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ZhangOff-equilibrium2025.xlsx
+++ b/public/downloads/ZhangOff-equilibrium2025.xlsx
@@ -1554,22 +1554,22 @@
         <v>8</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2113782624738079</v>
+        <v>-0.463656573794621</v>
       </c>
       <c r="O3" s="5">
         <v>3936</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8032404870340714</v>
+        <v>0.77796368269607</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6732179222643434</v>
+        <v>0.6099381609642034</v>
       </c>
       <c r="R3" s="5">
-        <v>3918</v>
+        <v>3832</v>
       </c>
       <c r="S3" s="5">
-        <v>18</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1613,16 +1613,16 @@
         <v>25</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.8155276813667445</v>
+        <v>-0.7971390531531029</v>
       </c>
       <c r="O4" s="5">
         <v>394</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7414454961892663</v>
+        <v>0.7450490948890712</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6001322194767448</v>
+        <v>0.5998131824263326</v>
       </c>
       <c r="R4" s="5">
         <v>389</v>
@@ -1795,22 +1795,22 @@
         <v>2488</v>
       </c>
       <c r="N3" s="4">
-        <v>-3.187690627829946</v>
+        <v>-3.625043404612143</v>
       </c>
       <c r="O3" s="5">
         <v>3367</v>
       </c>
       <c r="P3" s="4">
-        <v>1.336136711730304</v>
+        <v>1.242457599080184</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9560790932455088</v>
+        <v>0.7980054708485951</v>
       </c>
       <c r="R3" s="5">
-        <v>2694</v>
+        <v>2646</v>
       </c>
       <c r="S3" s="5">
-        <v>673</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1852,22 +1852,22 @@
         <v>111</v>
       </c>
       <c r="N4" s="4">
-        <v>-8.197244097329365</v>
+        <v>-7.962916990494591</v>
       </c>
       <c r="O4" s="5">
         <v>111</v>
       </c>
       <c r="P4" s="4">
-        <v>1.458867937463714</v>
+        <v>1.360429608595685</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.9250824191780832</v>
+        <v>0.8833359444345465</v>
       </c>
       <c r="R4" s="5">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="S4" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2034,22 +2034,22 @@
         <v>1929</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.283045460108345</v>
+        <v>-1.102923634710507</v>
       </c>
       <c r="O3" s="5">
         <v>7120</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6774416579413177</v>
+        <v>0.6887969367325224</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6574231414368105</v>
+        <v>0.6418047088470529</v>
       </c>
       <c r="R3" s="5">
-        <v>7112</v>
+        <v>7113</v>
       </c>
       <c r="S3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2093,22 +2093,22 @@
         <v>344</v>
       </c>
       <c r="N4" s="4">
-        <v>-5.03627796427779</v>
+        <v>-4.887398959040979</v>
       </c>
       <c r="O4" s="5">
         <v>348</v>
       </c>
       <c r="P4" s="4">
-        <v>1.360934442976052</v>
+        <v>1.403909681980716</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7068280366459635</v>
+        <v>0.6858330331663153</v>
       </c>
       <c r="R4" s="5">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S4" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3844146793413378</v>
+        <v>-0.407566721133918</v>
       </c>
       <c r="O3" s="5">
         <v>8249</v>
       </c>
       <c r="P3" s="4">
-        <v>0.300745106864395</v>
+        <v>0.2962661617963596</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2346293175403389</v>
+        <v>0.2337408842986914</v>
       </c>
       <c r="R3" s="5">
         <v>8249</v>
@@ -2332,16 +2332,16 @@
         <v>521</v>
       </c>
       <c r="N4" s="4">
-        <v>5.511207095576</v>
+        <v>5.481434956339626</v>
       </c>
       <c r="O4" s="5">
         <v>521</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5589266003509595</v>
+        <v>0.5580176472718392</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5212245269800118</v>
+        <v>0.5204912307654013</v>
       </c>
       <c r="R4" s="5">
         <v>521</v>
@@ -2514,16 +2514,16 @@
         <v>1410</v>
       </c>
       <c r="N3" s="4">
-        <v>1.451938877344592</v>
+        <v>1.465069796017332</v>
       </c>
       <c r="O3" s="5">
         <v>9405</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4220154667241661</v>
+        <v>0.421726993478751</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4183455764878601</v>
+        <v>0.4181748854263969</v>
       </c>
       <c r="R3" s="5">
         <v>9405</v>
@@ -2573,22 +2573,22 @@
         <v>469</v>
       </c>
       <c r="N4" s="4">
-        <v>4.134304405350816</v>
+        <v>4.162259147304553</v>
       </c>
       <c r="O4" s="5">
         <v>470</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8488539567798389</v>
+        <v>0.8455845038218952</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.803289567256825</v>
+        <v>0.8088345054615372</v>
       </c>
       <c r="R4" s="5">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="S4" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2755,16 +2755,16 @@
         <v>406</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.333578530714477</v>
+        <v>-1.316991333695244</v>
       </c>
       <c r="O3" s="5">
         <v>5131</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6131189730239349</v>
+        <v>0.6202328625056495</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3755385079974542</v>
+        <v>0.375333994433279</v>
       </c>
       <c r="R3" s="5">
         <v>5128</v>
@@ -2814,22 +2814,22 @@
         <v>403</v>
       </c>
       <c r="N4" s="4">
-        <v>-3.492783648038268</v>
+        <v>-3.684216591647669</v>
       </c>
       <c r="O4" s="5">
         <v>449</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9757129182466029</v>
+        <v>0.9093383979737875</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6715948100536716</v>
+        <v>0.6230826782611726</v>
       </c>
       <c r="R4" s="5">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="S4" s="5">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2996,22 +2996,22 @@
         <v>3565</v>
       </c>
       <c r="N3" s="4">
-        <v>1.711483991102156</v>
+        <v>1.727455516032592</v>
       </c>
       <c r="O3" s="5">
         <v>9867</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5510694338263112</v>
+        <v>0.5509095664072982</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5477384715728466</v>
+        <v>0.5479557045907947</v>
       </c>
       <c r="R3" s="5">
-        <v>9859</v>
+        <v>9861</v>
       </c>
       <c r="S3" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3231,16 +3231,16 @@
         <v>11</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5041476689181352</v>
+        <v>-0.4721421568733462</v>
       </c>
       <c r="O3" s="5">
         <v>9774</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2471684690726207</v>
+        <v>0.246398321860362</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2383586617098033</v>
+        <v>0.236879842585167</v>
       </c>
       <c r="R3" s="5">
         <v>9774</v>
@@ -3290,16 +3290,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.08546814202637566</v>
+        <v>0.07374221526515612</v>
       </c>
       <c r="O4" s="5">
         <v>659</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2248397046748344</v>
+        <v>0.223844995417105</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1871050905855445</v>
+        <v>0.1868262423315943</v>
       </c>
       <c r="R4" s="5">
         <v>659</v>
@@ -3472,16 +3472,16 @@
         <v>218</v>
       </c>
       <c r="N3" s="4">
-        <v>1.134845583634015</v>
+        <v>1.131045591085439</v>
       </c>
       <c r="O3" s="5">
         <v>4249</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4759429741647837</v>
+        <v>0.4770276495636022</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4205565030959294</v>
+        <v>0.420544009699178</v>
       </c>
       <c r="R3" s="5">
         <v>4249</v>
@@ -3531,16 +3531,16 @@
         <v>481</v>
       </c>
       <c r="N4" s="4">
-        <v>2.664383831707113</v>
+        <v>2.62267698168057</v>
       </c>
       <c r="O4" s="5">
         <v>519</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4988333099915616</v>
+        <v>0.4940864278112652</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3890546558856227</v>
+        <v>0.3875048203277943</v>
       </c>
       <c r="R4" s="5">
         <v>517</v>
@@ -3713,16 +3713,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03773676802866564</v>
+        <v>-0.2189369136043915</v>
       </c>
       <c r="O3" s="5">
         <v>7849</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6809044259481564</v>
+        <v>0.6564744462676547</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6223462387621174</v>
+        <v>0.6137448500114594</v>
       </c>
       <c r="R3" s="5">
         <v>7849</v>
@@ -3772,16 +3772,16 @@
         <v>99</v>
       </c>
       <c r="N4" s="4">
-        <v>1.513005900263611</v>
+        <v>1.51445281509848</v>
       </c>
       <c r="O4" s="5">
         <v>567</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4773051428671483</v>
+        <v>0.4774496035566146</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4265510716926407</v>
+        <v>0.4265510716926406</v>
       </c>
       <c r="R4" s="5">
         <v>566</v>
@@ -3900,13 +3900,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>83.9139344262295</v>
+        <v>83.92324888226528</v>
       </c>
       <c r="C3" s="3">
         <v>11.54061102831595</v>
       </c>
       <c r="D3" s="3">
-        <v>4.545454545454546</v>
+        <v>4.536140089418779</v>
       </c>
       <c r="E3" s="3">
         <v>1.024590163934426</v>
@@ -3915,16 +3915,16 @@
         <v>2.906110283159463</v>
       </c>
       <c r="G3" s="3">
-        <v>0.6147540983606558</v>
+        <v>0.6054396423248882</v>
       </c>
       <c r="H3" s="4">
-        <v>0.6115585570972248</v>
+        <v>0.6051322361287799</v>
       </c>
       <c r="I3" s="4">
-        <v>0.5491813127938447</v>
+        <v>0.5479707152852835</v>
       </c>
       <c r="J3" s="4">
-        <v>0.6517483021399869</v>
+        <v>0.6491446475847543</v>
       </c>
       <c r="K3" s="4">
         <v>94.26126542271162</v>
@@ -3950,13 +3950,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>55.73770491803278</v>
+        <v>55.82153502235469</v>
       </c>
       <c r="C4" s="3">
         <v>13.9623695976155</v>
       </c>
       <c r="D4" s="3">
-        <v>30.29992548435171</v>
+        <v>30.21609538002981</v>
       </c>
       <c r="E4" s="3">
         <v>24.69262295081967</v>
@@ -3965,16 +3965,16 @@
         <v>3.874813710879284</v>
       </c>
       <c r="G4" s="3">
-        <v>1.732488822652757</v>
+        <v>1.648658718330849</v>
       </c>
       <c r="H4" s="4">
-        <v>0.826994401907252</v>
+        <v>0.8292669837125023</v>
       </c>
       <c r="I4" s="4">
-        <v>0.7069916318878025</v>
+        <v>0.7087301684702568</v>
       </c>
       <c r="J4" s="4">
-        <v>1.008459968551259</v>
+        <v>1.017451306269075</v>
       </c>
       <c r="K4" s="4">
         <v>86.19680938694408</v>
@@ -4000,13 +4000,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>82.38636363636364</v>
+        <v>82.43293591654248</v>
       </c>
       <c r="C5" s="3">
         <v>15.58308494783905</v>
       </c>
       <c r="D5" s="3">
-        <v>2.030551415797317</v>
+        <v>1.98397913561848</v>
       </c>
       <c r="E5" s="3">
         <v>0.1956035767511178</v>
@@ -4015,16 +4015,16 @@
         <v>1.192250372578241</v>
       </c>
       <c r="G5" s="3">
-        <v>0.6426974664679582</v>
+        <v>0.5961251862891207</v>
       </c>
       <c r="H5" s="4">
-        <v>0.6254163401546194</v>
+        <v>0.6175787395413518</v>
       </c>
       <c r="I5" s="4">
-        <v>0.576275611808213</v>
+        <v>0.5707462235766633</v>
       </c>
       <c r="J5" s="4">
-        <v>1.031345925306566</v>
+        <v>1.017663417046672</v>
       </c>
       <c r="K5" s="4">
         <v>82.73282971907076</v>
@@ -4050,13 +4050,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>31.18479880774963</v>
+        <v>30.83084947839046</v>
       </c>
       <c r="C6" s="3">
         <v>48.15573770491803</v>
       </c>
       <c r="D6" s="3">
-        <v>20.65946348733234</v>
+        <v>21.0134128166915</v>
       </c>
       <c r="E6" s="3">
         <v>0.1210879284649776</v>
@@ -4065,16 +4065,16 @@
         <v>20.14716840536513</v>
       </c>
       <c r="G6" s="3">
-        <v>0.3912071535022355</v>
+        <v>0.7451564828614009</v>
       </c>
       <c r="H6" s="4">
-        <v>0.9787309435930821</v>
+        <v>1.04447535045982</v>
       </c>
       <c r="I6" s="4">
-        <v>0.8581527835101418</v>
+        <v>0.8338743656522356</v>
       </c>
       <c r="J6" s="4">
-        <v>1.300796609443142</v>
+        <v>1.387017171923629</v>
       </c>
       <c r="K6" s="4">
         <v>76.7875898496506</v>
@@ -4118,13 +4118,13 @@
         <v>0.01123595505617977</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2607768906587983</v>
+        <v>0.2606112568153988</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2297382668046554</v>
+        <v>0.2260562144756797</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2123045354288413</v>
+        <v>0.2104153450435285</v>
       </c>
       <c r="K7" s="4">
         <v>97.00264083161358</v>
@@ -4150,13 +4150,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>40.11736214605067</v>
+        <v>39.31631892697467</v>
       </c>
       <c r="C8" s="3">
         <v>54.96460506706408</v>
       </c>
       <c r="D8" s="3">
-        <v>4.918032786885246</v>
+        <v>5.719076005961251</v>
       </c>
       <c r="E8" s="3">
         <v>0.02794336810730253</v>
@@ -4165,16 +4165,16 @@
         <v>4.67585692995529</v>
       </c>
       <c r="G8" s="3">
-        <v>0.2142324888226528</v>
+        <v>1.015275707898659</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7990559715400165</v>
+        <v>0.7757348353287368</v>
       </c>
       <c r="I8" s="4">
-        <v>0.6666169614135479</v>
+        <v>0.6090050605967001</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8266286954237543</v>
+        <v>0.85644266298612</v>
       </c>
       <c r="K8" s="4">
         <v>91.3612919087157</v>
@@ -4200,13 +4200,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>25.88487332339791</v>
+        <v>25.41915052160954</v>
       </c>
       <c r="C9" s="3">
         <v>55.02049180327869</v>
       </c>
       <c r="D9" s="3">
-        <v>19.0946348733234</v>
+        <v>19.56035767511177</v>
       </c>
       <c r="E9" s="3">
         <v>0.3725782414307005</v>
@@ -4215,16 +4215,16 @@
         <v>12.21125186289121</v>
       </c>
       <c r="G9" s="3">
-        <v>6.510804769001491</v>
+        <v>6.976527570789866</v>
       </c>
       <c r="H9" s="4">
-        <v>1.344447591118175</v>
+        <v>1.250446202928709</v>
       </c>
       <c r="I9" s="4">
-        <v>0.9551310121747165</v>
+        <v>0.8006007179382376</v>
       </c>
       <c r="J9" s="4">
-        <v>17.12867365336112</v>
+        <v>17.17324931624623</v>
       </c>
       <c r="K9" s="4">
         <v>79.87936512160746</v>
@@ -4268,13 +4268,13 @@
         <v>0.456408345752608</v>
       </c>
       <c r="H10" s="4">
-        <v>0.7237251205642919</v>
+        <v>0.737221579597224</v>
       </c>
       <c r="I10" s="4">
-        <v>0.6594675278540107</v>
+        <v>0.6436206769346248</v>
       </c>
       <c r="J10" s="4">
-        <v>1.005838270807564</v>
+        <v>0.997904741577049</v>
       </c>
       <c r="K10" s="4">
         <v>90.41666349848437</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3182281495026898</v>
+        <v>0.3139909503526817</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2516550990817379</v>
+        <v>0.2507758820762462</v>
       </c>
       <c r="J11" s="4">
-        <v>0.292103242559304</v>
+        <v>0.2872752938417909</v>
       </c>
       <c r="K11" s="4">
         <v>89.92711913379345</v>
@@ -4350,13 +4350,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>91.81259314456037</v>
+        <v>91.83122205663189</v>
       </c>
       <c r="C12" s="3">
         <v>6.743666169895677</v>
       </c>
       <c r="D12" s="3">
-        <v>1.443740685543964</v>
+        <v>1.425111773472429</v>
       </c>
       <c r="E12" s="3">
         <v>0.1397168405365127</v>
@@ -4365,16 +4365,16 @@
         <v>1.136363636363636</v>
       </c>
       <c r="G12" s="3">
-        <v>0.1676602086438152</v>
+        <v>0.1490312965722802</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4509193026286439</v>
+        <v>0.4504289690766894</v>
       </c>
       <c r="I12" s="4">
-        <v>0.4359974669035618</v>
+        <v>0.4361644855375597</v>
       </c>
       <c r="J12" s="4">
-        <v>0.4701596700777561</v>
+        <v>0.4678162123713958</v>
       </c>
       <c r="K12" s="4">
         <v>87.33770669221499</v>
@@ -4400,13 +4400,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>51.66728763040238</v>
+        <v>51.62071535022355</v>
       </c>
       <c r="C13" s="3">
         <v>44.31818181818182</v>
       </c>
       <c r="D13" s="3">
-        <v>4.014530551415797</v>
+        <v>4.061102831594635</v>
       </c>
       <c r="E13" s="3">
         <v>0.1769746646795827</v>
@@ -4415,16 +4415,16 @@
         <v>3.530178837555887</v>
       </c>
       <c r="G13" s="3">
-        <v>0.3073770491803279</v>
+        <v>0.3539493293591655</v>
       </c>
       <c r="H13" s="4">
-        <v>0.6376724192028543</v>
+        <v>0.6398099605203045</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3979015133267413</v>
+        <v>0.3938413843836124</v>
       </c>
       <c r="J13" s="4">
-        <v>0.5504132639306648</v>
+        <v>0.5618144060168637</v>
       </c>
       <c r="K13" s="4">
         <v>91.56518661861153</v>
@@ -4450,13 +4450,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>91.83122205663189</v>
+        <v>91.84985096870342</v>
       </c>
       <c r="C14" s="3">
         <v>0.782414307004471</v>
       </c>
       <c r="D14" s="3">
-        <v>7.386363636363637</v>
+        <v>7.367734724292101</v>
       </c>
       <c r="E14" s="3">
         <v>6.790238450074515</v>
@@ -4465,16 +4465,16 @@
         <v>0.5216095380029807</v>
       </c>
       <c r="G14" s="3">
-        <v>0.07451564828614009</v>
+        <v>0.05588673621460507</v>
       </c>
       <c r="H14" s="4">
-        <v>1.505687824577747</v>
+        <v>1.505538782756128</v>
       </c>
       <c r="I14" s="4">
-        <v>0.5477384715728466</v>
+        <v>0.5479557045907947</v>
       </c>
       <c r="J14" s="4">
-        <v>1.114563672323896</v>
+        <v>1.114394775673883</v>
       </c>
       <c r="K14" s="4">
         <v>96.92511430801835</v>
@@ -4518,13 +4518,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2456564523329421</v>
+        <v>0.2448710986557935</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2351212320758642</v>
+        <v>0.2337182090600923</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3729896182993048</v>
+        <v>0.3735630076907889</v>
       </c>
       <c r="K15" s="4">
         <v>91.18416833946694</v>
@@ -4568,13 +4568,13 @@
         <v>0.01862891207153502</v>
       </c>
       <c r="H16" s="4">
-        <v>0.4774930183289108</v>
+        <v>0.4781828034184877</v>
       </c>
       <c r="I16" s="4">
-        <v>0.4171392863507073</v>
+        <v>0.4169600271341328</v>
       </c>
       <c r="J16" s="4">
-        <v>0.8082977110163694</v>
+        <v>0.8108675160051272</v>
       </c>
       <c r="K16" s="4">
         <v>90.55677952999359</v>
@@ -4618,13 +4618,13 @@
         <v>0.009314456035767511</v>
       </c>
       <c r="H17" s="4">
-        <v>0.6671174774757372</v>
+        <v>0.6443515829432391</v>
       </c>
       <c r="I17" s="4">
-        <v>0.6091768906264877</v>
+        <v>0.6011540385404611</v>
       </c>
       <c r="J17" s="4">
-        <v>0.5294219597422392</v>
+        <v>0.5310628690474305</v>
       </c>
       <c r="K17" s="4">
         <v>90.96431549519956</v>
@@ -5507,13 +5507,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>9009</v>
+        <v>9010</v>
       </c>
       <c r="C3" s="5">
         <v>1239</v>
       </c>
       <c r="D3" s="5">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E3" s="5">
         <v>110</v>
@@ -5522,7 +5522,7 @@
         <v>312</v>
       </c>
       <c r="G3" s="5">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="5">
         <v>110</v>
@@ -5551,13 +5551,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>5984</v>
+        <v>5993</v>
       </c>
       <c r="C4" s="5">
         <v>1499</v>
       </c>
       <c r="D4" s="5">
-        <v>3253</v>
+        <v>3244</v>
       </c>
       <c r="E4" s="5">
         <v>2651</v>
@@ -5566,7 +5566,7 @@
         <v>416</v>
       </c>
       <c r="G4" s="5">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H4" s="5">
         <v>2651</v>
@@ -5595,13 +5595,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>8845</v>
+        <v>8850</v>
       </c>
       <c r="C5" s="5">
         <v>1673</v>
       </c>
       <c r="D5" s="5">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E5" s="5">
         <v>21</v>
@@ -5610,7 +5610,7 @@
         <v>128</v>
       </c>
       <c r="G5" s="5">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H5" s="5">
         <v>21</v>
@@ -5639,13 +5639,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>3348</v>
+        <v>3310</v>
       </c>
       <c r="C6" s="5">
         <v>5170</v>
       </c>
       <c r="D6" s="5">
-        <v>2218</v>
+        <v>2256</v>
       </c>
       <c r="E6" s="5">
         <v>13</v>
@@ -5654,7 +5654,7 @@
         <v>2163</v>
       </c>
       <c r="G6" s="5">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="H6" s="5">
         <v>13</v>
@@ -5727,13 +5727,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>4307</v>
+        <v>4221</v>
       </c>
       <c r="C8" s="5">
         <v>5901</v>
       </c>
       <c r="D8" s="5">
-        <v>528</v>
+        <v>614</v>
       </c>
       <c r="E8" s="5">
         <v>3</v>
@@ -5742,7 +5742,7 @@
         <v>502</v>
       </c>
       <c r="G8" s="5">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="H8" s="5">
         <v>3</v>
@@ -5771,13 +5771,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>2779</v>
+        <v>2729</v>
       </c>
       <c r="C9" s="5">
         <v>5907</v>
       </c>
       <c r="D9" s="5">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="E9" s="5">
         <v>40</v>
@@ -5786,7 +5786,7 @@
         <v>1311</v>
       </c>
       <c r="G9" s="5">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="H9" s="5">
         <v>40</v>
@@ -5903,13 +5903,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>9857</v>
+        <v>9859</v>
       </c>
       <c r="C12" s="5">
         <v>724</v>
       </c>
       <c r="D12" s="5">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E12" s="5">
         <v>15</v>
@@ -5918,7 +5918,7 @@
         <v>122</v>
       </c>
       <c r="G12" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H12" s="5">
         <v>15</v>
@@ -5947,13 +5947,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5">
-        <v>5547</v>
+        <v>5542</v>
       </c>
       <c r="C13" s="5">
         <v>4758</v>
       </c>
       <c r="D13" s="5">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E13" s="5">
         <v>19</v>
@@ -5962,7 +5962,7 @@
         <v>379</v>
       </c>
       <c r="G13" s="5">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H13" s="5">
         <v>19</v>
@@ -5991,13 +5991,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>9859</v>
+        <v>9861</v>
       </c>
       <c r="C14" s="5">
         <v>84</v>
       </c>
       <c r="D14" s="5">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E14" s="5">
         <v>729</v>
@@ -6006,7 +6006,7 @@
         <v>56</v>
       </c>
       <c r="G14" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5">
         <v>729</v>
@@ -6321,22 +6321,22 @@
         <v>2275</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.55341118195192</v>
+        <v>-1.603302271738649</v>
       </c>
       <c r="O3" s="5">
         <v>8555</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5863262991227632</v>
+        <v>0.5793272197221919</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5327433027602524</v>
+        <v>0.5320148619065822</v>
       </c>
       <c r="R3" s="5">
-        <v>8525</v>
+        <v>8528</v>
       </c>
       <c r="S3" s="5">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6378,22 +6378,22 @@
         <v>520</v>
       </c>
       <c r="N4" s="4">
-        <v>5.961245578905347</v>
+        <v>5.914053248292703</v>
       </c>
       <c r="O4" s="5">
         <v>520</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9589446232132994</v>
+        <v>0.9604037756247064</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8387144440673466</v>
+        <v>0.8302767684254583</v>
       </c>
       <c r="R4" s="5">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="S4" s="5">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -6560,22 +6560,22 @@
         <v>4865</v>
       </c>
       <c r="N3" s="4">
-        <v>-2.885464126138628</v>
+        <v>-2.871169274374168</v>
       </c>
       <c r="O3" s="5">
         <v>5920</v>
       </c>
       <c r="P3" s="4">
-        <v>0.820886136153642</v>
+        <v>0.8216854642351348</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7185852724925366</v>
+        <v>0.7204669492830975</v>
       </c>
       <c r="R3" s="5">
-        <v>5736</v>
+        <v>5745</v>
       </c>
       <c r="S3" s="5">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6619,16 +6619,16 @@
         <v>236</v>
       </c>
       <c r="N4" s="4">
-        <v>2.862357054948811</v>
+        <v>2.909170520029022</v>
       </c>
       <c r="O4" s="5">
         <v>250</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9110901817255218</v>
+        <v>0.9336458399009092</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4388419443524996</v>
+        <v>0.4368438548824758</v>
       </c>
       <c r="R4" s="5">
         <v>248</v>
@@ -6801,22 +6801,22 @@
         <v>80</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2899343001694845</v>
+        <v>-0.3720942454785927</v>
       </c>
       <c r="O3" s="5">
         <v>8607</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5918375238299109</v>
+        <v>0.5816435071347517</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5659406809410051</v>
+        <v>0.5609011014636268</v>
       </c>
       <c r="R3" s="5">
-        <v>8570</v>
+        <v>8576</v>
       </c>
       <c r="S3" s="5">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6858,22 +6858,22 @@
         <v>307</v>
       </c>
       <c r="N4" s="4">
-        <v>9.143691949241109</v>
+        <v>8.990091830937445</v>
       </c>
       <c r="O4" s="5">
         <v>307</v>
       </c>
       <c r="P4" s="4">
-        <v>1.087713964080351</v>
+        <v>1.112318411009934</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8983496391971995</v>
+        <v>0.878891359494186</v>
       </c>
       <c r="R4" s="5">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S4" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -7040,22 +7040,22 @@
         <v>1413</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.909523165613009</v>
+        <v>-1.685543133586521</v>
       </c>
       <c r="O3" s="5">
         <v>3236</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9798017391225705</v>
+        <v>1.050886744375467</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8578885945442692</v>
+        <v>0.8326711608477678</v>
       </c>
       <c r="R3" s="5">
-        <v>3218</v>
+        <v>3180</v>
       </c>
       <c r="S3" s="5">
-        <v>18</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7097,16 +7097,16 @@
         <v>154</v>
       </c>
       <c r="N4" s="4">
-        <v>5.721900252584998</v>
+        <v>5.634613421264362</v>
       </c>
       <c r="O4" s="5">
         <v>154</v>
       </c>
       <c r="P4" s="4">
-        <v>0.963988725636205</v>
+        <v>0.9562062422043704</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8646924765268945</v>
+        <v>0.8633066062538354</v>
       </c>
       <c r="R4" s="5">
         <v>130</v>
@@ -7279,16 +7279,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3567219073480565</v>
+        <v>0.4182821622197324</v>
       </c>
       <c r="O3" s="5">
         <v>6878</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2663381972943886</v>
+        <v>0.2661276708704862</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2371016195117367</v>
+        <v>0.2330924366469607</v>
       </c>
       <c r="R3" s="5">
         <v>6878</v>
@@ -7338,16 +7338,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>1.161887410235063</v>
+        <v>1.17213322024736</v>
       </c>
       <c r="O4" s="5">
         <v>662</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1982561765835863</v>
+        <v>0.1985952292057294</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1531192956710621</v>
+        <v>0.1528411825633186</v>
       </c>
       <c r="R4" s="5">
         <v>661</v>
